--- a/research/traditional_assets/database/data/bermuda/bermuda_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_reinsurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.12225</v>
+        <v>0.134</v>
       </c>
       <c r="E2">
-        <v>0.103715</v>
+        <v>0.144</v>
       </c>
       <c r="F2">
-        <v>2.693</v>
+        <v>0.916</v>
       </c>
       <c r="G2">
-        <v>0.1205874894154764</v>
+        <v>0.0114998241449046</v>
       </c>
       <c r="H2">
-        <v>0.1205874894154764</v>
+        <v>0.0114998241449046</v>
       </c>
       <c r="I2">
-        <v>0.1092688119930945</v>
+        <v>-0.09328495135704365</v>
       </c>
       <c r="J2">
-        <v>0.1065441605275471</v>
+        <v>-0.08963413474295462</v>
       </c>
       <c r="K2">
-        <v>2481.348</v>
+        <v>-2373.22</v>
       </c>
       <c r="L2">
-        <v>0.1066553765081603</v>
+        <v>-0.08694642281426772</v>
       </c>
       <c r="M2">
-        <v>2148.832</v>
+        <v>1256.595</v>
       </c>
       <c r="N2">
-        <v>0.08170482518211068</v>
+        <v>0.04388917781334906</v>
       </c>
       <c r="O2">
-        <v>0.8659938065922232</v>
+        <v>-0.529489470002781</v>
       </c>
       <c r="P2">
-        <v>318.1</v>
+        <v>409.235</v>
       </c>
       <c r="Q2">
-        <v>0.01209508462756949</v>
+        <v>0.01429337828214015</v>
       </c>
       <c r="R2">
-        <v>0.1281964480596837</v>
+        <v>-0.1724387119609644</v>
       </c>
       <c r="S2">
-        <v>1830.732</v>
+        <v>847.36</v>
       </c>
       <c r="T2">
-        <v>0.8519660913463687</v>
+        <v>0.674330233687067</v>
       </c>
       <c r="U2">
-        <v>5270.3</v>
+        <v>8121.4</v>
       </c>
       <c r="V2">
-        <v>0.2003920921492597</v>
+        <v>0.2836566822988576</v>
       </c>
       <c r="W2">
-        <v>0.2040487531521435</v>
+        <v>-0.0874495483374976</v>
       </c>
       <c r="X2">
-        <v>0.1121603868461994</v>
+        <v>0.1883143918527734</v>
       </c>
       <c r="Y2">
-        <v>0.09188836630594406</v>
+        <v>-0.275763940190271</v>
       </c>
       <c r="Z2">
-        <v>0.9244159297964781</v>
+        <v>0.9261888044736549</v>
       </c>
       <c r="AA2">
-        <v>0.1099408706094689</v>
+        <v>-0.09871386171265252</v>
       </c>
       <c r="AB2">
-        <v>0.0913433572307053</v>
+        <v>0.1334417017938161</v>
       </c>
       <c r="AC2">
-        <v>0.02259031158573373</v>
+        <v>-0.218236818261605</v>
       </c>
       <c r="AD2">
-        <v>5838.7</v>
+        <v>13565.9</v>
       </c>
       <c r="AE2">
-        <v>261.0508104972889</v>
+        <v>222.3720214038894</v>
       </c>
       <c r="AF2">
-        <v>6099.750810497289</v>
+        <v>13788.27202140389</v>
       </c>
       <c r="AG2">
-        <v>829.4508104972892</v>
+        <v>5666.872021403889</v>
       </c>
       <c r="AH2">
-        <v>0.1882657105024289</v>
+        <v>0.3250466618155791</v>
       </c>
       <c r="AI2">
-        <v>0.1643289428047013</v>
+        <v>0.3526351673407589</v>
       </c>
       <c r="AJ2">
-        <v>0.03057388263124384</v>
+        <v>0.1652247447783468</v>
       </c>
       <c r="AK2">
-        <v>0.02604335131061949</v>
+        <v>0.1829246348167443</v>
       </c>
       <c r="AL2">
-        <v>226.493</v>
+        <v>444.9</v>
       </c>
       <c r="AM2">
-        <v>226.493</v>
+        <v>444.9</v>
       </c>
       <c r="AN2">
-        <v>5.32136731260333</v>
+        <v>-4.60449612029479</v>
       </c>
       <c r="AO2">
-        <v>11.28437523455471</v>
+        <v>-5.713526635198921</v>
       </c>
       <c r="AP2">
-        <v>0.7559580780640578</v>
+        <v>-1.923432299866674</v>
       </c>
       <c r="AQ2">
-        <v>11.28437523455471</v>
+        <v>-5.713526635198921</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brookfield Asset Management Reinsurance Partners Ltd. (NYSE:BAMR)</t>
+          <t>American Overseas Group Limited (OTCPK:AORE.F)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,101 +724,107 @@
           <t>Reinsurance</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0124</v>
+      </c>
       <c r="G3">
-        <v>0.0009820341047503047</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.0009820341047503047</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>9.211327649208283e-05</v>
+        <v>0.005744255078350416</v>
       </c>
       <c r="J3">
-        <v>9.211327649208283e-05</v>
+        <v>0.005744255078350416</v>
       </c>
       <c r="K3">
-        <v>0.608</v>
+        <v>-1.76</v>
       </c>
       <c r="L3">
-        <v>0.0002314250913520098</v>
+        <v>-0.05365853658536586</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.003441550992313869</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>9.868421052631579</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.0005735918320523115</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>1.644736842105263</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>5</v>
-      </c>
-      <c r="T3">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>406</v>
+        <v>22.7</v>
       </c>
       <c r="V3">
-        <v>0.2328782838132385</v>
+        <v>2.391991570073762</v>
+      </c>
+      <c r="W3">
+        <v>-0.04512820512820513</v>
       </c>
       <c r="X3">
-        <v>0.08483189729771703</v>
+        <v>0.2709565010563562</v>
+      </c>
+      <c r="Y3">
+        <v>-0.3160847061845614</v>
       </c>
       <c r="AB3">
-        <v>0.08483189729771703</v>
+        <v>0.201719857147425</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.322942167150532</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>17.82294216715053</v>
       </c>
       <c r="AG3">
-        <v>-406</v>
+        <v>-4.877057832849466</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.6525456707694535</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.3251000669174209</v>
       </c>
       <c r="AJ3">
-        <v>-0.3035740989980559</v>
+        <v>-1.057255360273047</v>
       </c>
       <c r="AK3">
-        <v>-0.4655963302752293</v>
+        <v>-0.1518247552628236</v>
       </c>
       <c r="AL3">
-        <v>0.093</v>
+        <v>1.8</v>
       </c>
       <c r="AM3">
-        <v>0.093</v>
+        <v>1.8</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>44.4743935309973</v>
       </c>
       <c r="AO3">
-        <v>2.602150537634409</v>
+        <v>0.04555555555555556</v>
       </c>
       <c r="AP3">
-        <v>-513.9240506329114</v>
+        <v>-13.14570844433818</v>
       </c>
       <c r="AQ3">
-        <v>2.602150537634409</v>
+        <v>0.04555555555555556</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SiriusPoint Ltd. (NYSE:SPNT)</t>
+          <t>Brookfield Reinsurance Ltd. (NYSE:BNRE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,122 +843,116 @@
           <t>Reinsurance</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.237</v>
-      </c>
-      <c r="E4">
-        <v>0.201</v>
-      </c>
       <c r="G4">
+        <v>0.002595437616387337</v>
+      </c>
+      <c r="H4">
+        <v>0.002595437616387337</v>
+      </c>
+      <c r="I4">
+        <v>0.04667132216014898</v>
+      </c>
+      <c r="J4">
+        <v>0.03951079054105763</v>
+      </c>
+      <c r="K4">
+        <v>307</v>
+      </c>
+      <c r="L4">
+        <v>0.03573091247672253</v>
+      </c>
+      <c r="M4">
+        <v>32.13500000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.02246417336595596</v>
+      </c>
+      <c r="O4">
+        <v>0.1046742671009772</v>
+      </c>
+      <c r="P4">
+        <v>25.13500000000001</v>
+      </c>
+      <c r="Q4">
+        <v>0.01757077944774555</v>
+      </c>
+      <c r="R4">
+        <v>0.08187296416938113</v>
+      </c>
+      <c r="S4">
+        <v>7</v>
+      </c>
+      <c r="T4">
+        <v>0.2178310253617551</v>
+      </c>
+      <c r="U4">
+        <v>3153</v>
+      </c>
+      <c r="V4">
+        <v>2.204124432016777</v>
+      </c>
+      <c r="W4">
+        <v>0.2402190923317684</v>
+      </c>
+      <c r="X4">
+        <v>0.4554265980511781</v>
+      </c>
+      <c r="Y4">
+        <v>-0.2152075057194097</v>
+      </c>
+      <c r="Z4">
+        <v>9.853211009174313</v>
+      </c>
+      <c r="AA4">
+        <v>0.3893081563403293</v>
+      </c>
+      <c r="AB4">
+        <v>0.1346675300480364</v>
+      </c>
+      <c r="AC4">
+        <v>0.2546406262922929</v>
+      </c>
+      <c r="AD4">
+        <v>5958</v>
+      </c>
+      <c r="AE4">
         <v>0</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0.1725037014268196</v>
-      </c>
-      <c r="J4">
-        <v>0.1666960768121167</v>
-      </c>
-      <c r="K4">
-        <v>291.3</v>
-      </c>
-      <c r="L4">
-        <v>0.1379849367628251</v>
-      </c>
-      <c r="M4">
-        <v>0.302</v>
-      </c>
-      <c r="N4">
-        <v>0.0002332586699621534</v>
-      </c>
-      <c r="O4">
-        <v>0.001036731891520769</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
-      <c r="S4">
-        <v>0.302</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
-      </c>
-      <c r="U4">
-        <v>701.2</v>
-      </c>
-      <c r="V4">
-        <v>0.5415926469452383</v>
-      </c>
-      <c r="W4">
-        <v>0.2040487531521435</v>
-      </c>
-      <c r="X4">
-        <v>0.1294193341597848</v>
-      </c>
-      <c r="Y4">
-        <v>0.07462941899235864</v>
-      </c>
-      <c r="Z4">
-        <v>2.051908234654355</v>
-      </c>
-      <c r="AA4">
-        <v>0.3420450526953571</v>
-      </c>
-      <c r="AB4">
-        <v>0.09385171131453099</v>
-      </c>
-      <c r="AC4">
-        <v>0.2481933413808261</v>
-      </c>
-      <c r="AD4">
-        <v>827</v>
-      </c>
-      <c r="AE4">
-        <v>0.8471795892059562</v>
-      </c>
       <c r="AF4">
-        <v>827.847179589206</v>
+        <v>5958</v>
       </c>
       <c r="AG4">
-        <v>126.647179589206</v>
+        <v>2805</v>
       </c>
       <c r="AH4">
-        <v>0.3900253372692644</v>
+        <v>0.8063883061514516</v>
       </c>
       <c r="AI4">
-        <v>0.2388585349245917</v>
+        <v>0.8998640688717716</v>
       </c>
       <c r="AJ4">
-        <v>0.08910362042988625</v>
+        <v>0.6622594734978161</v>
       </c>
       <c r="AK4">
-        <v>0.04580952698927183</v>
+        <v>0.8088235294117647</v>
       </c>
       <c r="AL4">
-        <v>26.4</v>
+        <v>122</v>
       </c>
       <c r="AM4">
-        <v>26.4</v>
+        <v>122</v>
       </c>
       <c r="AN4">
-        <v>982.1852731591449</v>
+        <v>14.31867339581831</v>
       </c>
       <c r="AO4">
-        <v>13.76893939393939</v>
+        <v>3.286885245901639</v>
       </c>
       <c r="AP4">
-        <v>150.412327303095</v>
+        <v>6.741167988464311</v>
       </c>
       <c r="AQ4">
-        <v>13.76893939393939</v>
+        <v>3.286885245901639</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enstar Group Limited (NasdaqGS:ESGR)</t>
+          <t>Everest Re Group, Ltd. (NYSE:RE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,121 +972,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.09449999999999999</v>
+        <v>0.134</v>
       </c>
       <c r="E5">
-        <v>0.281</v>
+        <v>0.144</v>
+      </c>
+      <c r="F5">
+        <v>0.167</v>
       </c>
       <c r="G5">
-        <v>1.047870004391743</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>1.047870004391743</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.6909985119420532</v>
+        <v>0.05712112050887563</v>
       </c>
       <c r="J5">
-        <v>0.6843994649681812</v>
+        <v>0.05712112050887563</v>
       </c>
       <c r="K5">
-        <v>1222.9</v>
+        <v>532.1</v>
       </c>
       <c r="L5">
-        <v>0.7672375933245499</v>
+        <v>0.0443283681562198</v>
       </c>
       <c r="M5">
-        <v>890.7</v>
+        <v>357.9</v>
       </c>
       <c r="N5">
-        <v>0.2018766573740396</v>
+        <v>0.0275855158699573</v>
       </c>
       <c r="O5">
-        <v>0.7283506419167552</v>
+        <v>0.6726179289607216</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>251.7</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.01940004007954247</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.4730313850779928</v>
       </c>
       <c r="S5">
-        <v>890.7</v>
+        <v>106.2</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0.2967309304274937</v>
       </c>
       <c r="U5">
-        <v>1587.2</v>
+        <v>1679</v>
       </c>
       <c r="V5">
-        <v>0.3597379932458467</v>
+        <v>0.1294106765735074</v>
       </c>
       <c r="W5">
-        <v>0.2133424050522496</v>
+        <v>0.05332411360311066</v>
       </c>
       <c r="X5">
-        <v>0.1121603868461994</v>
+        <v>0.1395809498475814</v>
       </c>
       <c r="Y5">
-        <v>0.1011820182060502</v>
+        <v>-0.08625683624447075</v>
       </c>
       <c r="Z5">
-        <v>0.2413669790345039</v>
+        <v>1.093940924793924</v>
       </c>
       <c r="AA5">
-        <v>0.1651914313122007</v>
+        <v>0.06248713139474459</v>
       </c>
       <c r="AB5">
-        <v>0.0913433572307053</v>
+        <v>0.1232273068909808</v>
       </c>
       <c r="AC5">
-        <v>0.07384807408149541</v>
+        <v>-0.06074017549623621</v>
       </c>
       <c r="AD5">
-        <v>1690.7</v>
+        <v>3084</v>
       </c>
       <c r="AE5">
-        <v>38.43735907780653</v>
+        <v>151.7045892983024</v>
       </c>
       <c r="AF5">
-        <v>1729.137359077807</v>
+        <v>3235.704589298302</v>
       </c>
       <c r="AG5">
-        <v>141.9373590778066</v>
+        <v>1556.704589298302</v>
       </c>
       <c r="AH5">
-        <v>0.2815617208675127</v>
+        <v>0.199612809037414</v>
       </c>
       <c r="AI5">
-        <v>0.210420383080784</v>
+        <v>0.2972707768734123</v>
       </c>
       <c r="AJ5">
-        <v>0.03116736818042901</v>
+        <v>0.1071306042739267</v>
       </c>
       <c r="AK5">
-        <v>0.02140726050439585</v>
+        <v>0.169102166401036</v>
       </c>
       <c r="AL5">
-        <v>67.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AM5">
-        <v>67.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AN5">
-        <v>1.429320212703002</v>
+        <v>147.5598086124402</v>
       </c>
       <c r="AO5">
-        <v>16.28592592592593</v>
+        <v>7.158599382080331</v>
       </c>
       <c r="AP5">
-        <v>0.1199940475942467</v>
+        <v>74.48347317216758</v>
       </c>
       <c r="AQ5">
-        <v>16.28592592592593</v>
+        <v>7.158599382080331</v>
       </c>
     </row>
     <row r="6">
@@ -1097,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Everest Re Group, Ltd. (NYSE:RE)</t>
+          <t>Maiden Holdings, Ltd. (NasdaqCM:MHLD)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1106,124 +1109,118 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.15</v>
-      </c>
-      <c r="E6">
-        <v>0.00643</v>
-      </c>
-      <c r="F6">
-        <v>0.6759999999999999</v>
+        <v>-0.4970000000000001</v>
       </c>
       <c r="G6">
+        <v>0.4625850340136055</v>
+      </c>
+      <c r="H6">
+        <v>0.4625850340136055</v>
+      </c>
+      <c r="I6">
+        <v>0.02816326530612245</v>
+      </c>
+      <c r="J6">
+        <v>0.02256438114814271</v>
+      </c>
+      <c r="K6">
+        <v>3.34</v>
+      </c>
+      <c r="L6">
+        <v>0.0454421768707483</v>
+      </c>
+      <c r="M6">
+        <v>1.06</v>
+      </c>
+      <c r="N6">
+        <v>0.00576400217509516</v>
+      </c>
+      <c r="O6">
+        <v>0.3173652694610778</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>1.06</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>24.4</v>
+      </c>
+      <c r="V6">
+        <v>0.1326808047852093</v>
+      </c>
+      <c r="W6">
+        <v>0.0154772937905468</v>
+      </c>
+      <c r="X6">
+        <v>0.2315333633803699</v>
+      </c>
+      <c r="Y6">
+        <v>-0.2160560695898231</v>
+      </c>
+      <c r="Z6">
+        <v>0.1206500328299409</v>
+      </c>
+      <c r="AA6">
+        <v>0.002722393326310717</v>
+      </c>
+      <c r="AB6">
+        <v>0.1349043362361488</v>
+      </c>
+      <c r="AC6">
+        <v>-0.1321819429098381</v>
+      </c>
+      <c r="AD6">
+        <v>255.5</v>
+      </c>
+      <c r="AE6">
         <v>0</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0.1050332367296777</v>
-      </c>
-      <c r="J6">
-        <v>0.09123917216346247</v>
-      </c>
-      <c r="K6">
-        <v>1012</v>
-      </c>
-      <c r="L6">
-        <v>0.08793500456184559</v>
-      </c>
-      <c r="M6">
-        <v>463.5</v>
-      </c>
-      <c r="N6">
-        <v>0.0429803412462908</v>
-      </c>
-      <c r="O6">
-        <v>0.45800395256917</v>
-      </c>
-      <c r="P6">
-        <v>247.7</v>
-      </c>
-      <c r="Q6">
-        <v>0.02296921364985163</v>
-      </c>
-      <c r="R6">
-        <v>0.2447628458498024</v>
-      </c>
-      <c r="S6">
-        <v>215.8</v>
-      </c>
-      <c r="T6">
-        <v>0.4655879180151025</v>
-      </c>
-      <c r="U6">
-        <v>1068.4</v>
-      </c>
-      <c r="V6">
-        <v>0.09907270029673591</v>
-      </c>
-      <c r="W6">
-        <v>0.1055122871769208</v>
-      </c>
-      <c r="X6">
-        <v>0.0984014566511148</v>
-      </c>
-      <c r="Y6">
-        <v>0.007110830525805967</v>
-      </c>
-      <c r="Z6">
-        <v>1.204974442474125</v>
-      </c>
-      <c r="AA6">
-        <v>0.1099408706094689</v>
-      </c>
-      <c r="AB6">
-        <v>0.08735055902373515</v>
-      </c>
-      <c r="AC6">
-        <v>0.02259031158573373</v>
-      </c>
-      <c r="AD6">
-        <v>1910.9</v>
-      </c>
-      <c r="AE6">
-        <v>187.6249754825236</v>
-      </c>
       <c r="AF6">
-        <v>2098.524975482524</v>
+        <v>255.5</v>
       </c>
       <c r="AG6">
-        <v>1030.124975482523</v>
+        <v>231.1</v>
       </c>
       <c r="AH6">
-        <v>0.1628970236406564</v>
+        <v>0.581474738279472</v>
       </c>
       <c r="AI6">
-        <v>0.1737603096550452</v>
+        <v>0.4383256133127466</v>
       </c>
       <c r="AJ6">
-        <v>0.08719435232150574</v>
+        <v>0.5568674698795181</v>
       </c>
       <c r="AK6">
-        <v>0.09357350445003483</v>
+        <v>0.4137869292748433</v>
       </c>
       <c r="AL6">
-        <v>61.6</v>
+        <v>19.3</v>
       </c>
       <c r="AM6">
-        <v>61.6</v>
+        <v>19.3</v>
       </c>
       <c r="AN6">
-        <v>103.2918918918919</v>
+        <v>52.35655737704918</v>
       </c>
       <c r="AO6">
-        <v>19.93181818181818</v>
+        <v>0.1072538860103627</v>
       </c>
       <c r="AP6">
-        <v>55.68243110716343</v>
+        <v>47.35655737704918</v>
       </c>
       <c r="AQ6">
-        <v>19.93181818181818</v>
+        <v>0.1072538860103627</v>
       </c>
     </row>
     <row r="7">
@@ -1234,7 +1231,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maiden Holdings, Ltd. (NasdaqCM:MHLD)</t>
+          <t>Conduit Holdings Limited (LSE:CRE)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1242,122 +1239,110 @@
           <t>Reinsurance</t>
         </is>
       </c>
-      <c r="D7">
-        <v>-0.469</v>
-      </c>
-      <c r="E7">
-        <v>-0.307</v>
-      </c>
       <c r="G7">
-        <v>0.6240070609002648</v>
+        <v>-0.1351619299405155</v>
       </c>
       <c r="H7">
-        <v>0.6240070609002648</v>
+        <v>-0.1351619299405155</v>
       </c>
       <c r="I7">
-        <v>0.3071603085223259</v>
+        <v>-0.2967614011896893</v>
       </c>
       <c r="J7">
-        <v>0.3071603085223259</v>
+        <v>-0.2967614011896893</v>
       </c>
       <c r="K7">
-        <v>23.8</v>
+        <v>-91</v>
       </c>
       <c r="L7">
-        <v>0.2100617828773169</v>
+        <v>-0.3007270323859881</v>
       </c>
       <c r="M7">
-        <v>2.43</v>
+        <v>62.6</v>
       </c>
       <c r="N7">
-        <v>0.009187145557655955</v>
+        <v>0.07580527972874788</v>
       </c>
       <c r="O7">
-        <v>0.1021008403361345</v>
+        <v>-0.6879120879120879</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>59.4</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.07193024945507387</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>-0.6527472527472528</v>
       </c>
       <c r="S7">
-        <v>2.43</v>
+        <v>3.200000000000003</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>0.05111821086261985</v>
       </c>
       <c r="U7">
-        <v>29.3</v>
+        <v>92</v>
       </c>
       <c r="V7">
-        <v>0.1107750472589792</v>
+        <v>0.1114071203681279</v>
       </c>
       <c r="W7">
-        <v>0.3255813953488372</v>
+        <v>-0.0874495483374976</v>
       </c>
       <c r="X7">
-        <v>0.1525940821010247</v>
+        <v>0.1197177482092605</v>
       </c>
       <c r="Y7">
-        <v>0.1729873132478125</v>
+        <v>-0.2071672965467581</v>
       </c>
       <c r="Z7">
-        <v>0.1611140193523479</v>
+        <v>0.3326371331208091</v>
       </c>
       <c r="AA7">
-        <v>0.04948783189153918</v>
+        <v>-0.09871386171265252</v>
       </c>
       <c r="AB7">
-        <v>0.09622935937326742</v>
+        <v>0.1195229565489525</v>
       </c>
       <c r="AC7">
-        <v>-0.04674152748172824</v>
+        <v>-0.218236818261605</v>
       </c>
       <c r="AD7">
-        <v>255.3</v>
+        <v>2.6</v>
       </c>
       <c r="AE7">
-        <v>1.728685222102354</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>257.0286852221024</v>
+        <v>2.6</v>
       </c>
       <c r="AG7">
-        <v>227.7286852221023</v>
+        <v>-89.40000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.492837100825321</v>
+        <v>0.003138580395943989</v>
       </c>
       <c r="AI7">
-        <v>0.4014638693249683</v>
+        <v>0.002920035938903864</v>
       </c>
       <c r="AJ7">
-        <v>0.4626481390846759</v>
+        <v>-0.121401412275937</v>
       </c>
       <c r="AK7">
-        <v>0.3727582134063845</v>
+        <v>-0.1119739478957916</v>
       </c>
       <c r="AL7">
-        <v>19.3</v>
+        <v>0.5</v>
       </c>
       <c r="AM7">
-        <v>19.3</v>
-      </c>
-      <c r="AN7">
-        <v>6.327608000594839</v>
+        <v>0.5</v>
       </c>
       <c r="AO7">
-        <v>1.77720207253886</v>
-      </c>
-      <c r="AP7">
-        <v>5.644253233749779</v>
+        <v>-179.6</v>
       </c>
       <c r="AQ7">
-        <v>1.77720207253886</v>
+        <v>-179.6</v>
       </c>
     </row>
     <row r="8">
@@ -1368,7 +1353,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RenaissanceRe Holdings Ltd. (NYSE:RNR)</t>
+          <t>Enstar Group Limited (NasdaqGS:ESGR)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1376,122 +1361,101 @@
           <t>Reinsurance</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.246</v>
-      </c>
-      <c r="F8">
-        <v>4.71</v>
-      </c>
-      <c r="G8">
-        <v>0.2010373679627456</v>
-      </c>
-      <c r="H8">
-        <v>0.2010373679627456</v>
-      </c>
-      <c r="I8">
-        <v>-0.0306321944153907</v>
-      </c>
-      <c r="J8">
-        <v>-0.0306321944153907</v>
-      </c>
       <c r="K8">
-        <v>-62.8</v>
-      </c>
-      <c r="L8">
-        <v>-0.01188808541248627</v>
+        <v>-1111</v>
       </c>
       <c r="M8">
-        <v>785.9</v>
+        <v>215</v>
       </c>
       <c r="N8">
-        <v>0.1008533846647417</v>
+        <v>0.05466564963132469</v>
       </c>
       <c r="O8">
-        <v>-12.51433121019108</v>
+        <v>-0.1935193519351935</v>
       </c>
       <c r="P8">
-        <v>69.40000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.008905999358357395</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>-1.105095541401274</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>716.5</v>
+        <v>215</v>
       </c>
       <c r="T8">
-        <v>0.9116935996946176</v>
+        <v>1</v>
       </c>
       <c r="U8">
-        <v>1440.7</v>
+        <v>923</v>
       </c>
       <c r="V8">
-        <v>0.1848829002245749</v>
+        <v>0.2346809051614544</v>
       </c>
       <c r="W8">
-        <v>-0.009146785516618601</v>
+        <v>-0.185444833917543</v>
       </c>
       <c r="X8">
-        <v>0.09528956242832477</v>
+        <v>0.1585343390611268</v>
       </c>
       <c r="Y8">
-        <v>-0.1044363479449434</v>
+        <v>-0.3439791729786699</v>
       </c>
       <c r="Z8">
-        <v>0.7266461632581541</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>-0.0222587665441215</v>
+        <v>-0.1812947778694225</v>
       </c>
       <c r="AB8">
-        <v>0.08745050148848865</v>
+        <v>0.1293686485451029</v>
       </c>
       <c r="AC8">
-        <v>-0.1097092680326102</v>
+        <v>-0.3106634264145254</v>
       </c>
       <c r="AD8">
-        <v>1138.3</v>
+        <v>1905</v>
       </c>
       <c r="AE8">
-        <v>30.33815109371442</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1168.638151093714</v>
+        <v>1905</v>
       </c>
       <c r="AG8">
-        <v>-272.0618489062856</v>
+        <v>982</v>
       </c>
       <c r="AH8">
-        <v>0.1304117994153546</v>
+        <v>0.3263103802672148</v>
       </c>
       <c r="AI8">
-        <v>0.1027244323374943</v>
+        <v>0.3058275806710548</v>
       </c>
       <c r="AJ8">
-        <v>-0.03617632954892648</v>
+        <v>0.1997965412004069</v>
       </c>
       <c r="AK8">
-        <v>-0.02738214763402731</v>
+        <v>0.185073501696193</v>
       </c>
       <c r="AL8">
-        <v>49.8</v>
+        <v>89</v>
       </c>
       <c r="AM8">
-        <v>49.8</v>
+        <v>89</v>
       </c>
       <c r="AN8">
-        <v>-7.772618641174462</v>
+        <v>-1.788732394366197</v>
       </c>
       <c r="AO8">
-        <v>-3.293172690763052</v>
+        <v>-12.59550561797753</v>
       </c>
       <c r="AP8">
-        <v>1.857711498165146</v>
+        <v>-0.9220657276995305</v>
       </c>
       <c r="AQ8">
-        <v>-3.293172690763052</v>
+        <v>-12.59550561797753</v>
       </c>
     </row>
     <row r="9">
@@ -1502,7 +1466,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Overseas Group Limited (OTCPK:AORE.F)</t>
+          <t>RenaissanceRe Holdings Ltd. (NYSE:RNR)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1511,115 +1475,365 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.00228</v>
+        <v>0.181</v>
+      </c>
+      <c r="F9">
+        <v>1.665</v>
       </c>
       <c r="G9">
+        <v>-0.001465501951046471</v>
+      </c>
+      <c r="H9">
+        <v>-0.001465501951046471</v>
+      </c>
+      <c r="I9">
+        <v>-0.3272404727676074</v>
+      </c>
+      <c r="J9">
+        <v>-0.3272404727676074</v>
+      </c>
+      <c r="K9">
+        <v>-1298.4</v>
+      </c>
+      <c r="L9">
+        <v>-0.287868038311458</v>
+      </c>
+      <c r="M9">
+        <v>567.5</v>
+      </c>
+      <c r="N9">
+        <v>0.07048638712241653</v>
+      </c>
+      <c r="O9">
+        <v>-0.4370764017252002</v>
+      </c>
+      <c r="P9">
+        <v>64.7</v>
+      </c>
+      <c r="Q9">
+        <v>0.008036069157392687</v>
+      </c>
+      <c r="R9">
+        <v>-0.0498305606900801</v>
+      </c>
+      <c r="S9">
+        <v>502.8</v>
+      </c>
+      <c r="T9">
+        <v>0.8859911894273128</v>
+      </c>
+      <c r="U9">
+        <v>1204.2</v>
+      </c>
+      <c r="V9">
+        <v>0.1495677662957075</v>
+      </c>
+      <c r="W9">
+        <v>-0.2164180348362364</v>
+      </c>
+      <c r="X9">
+        <v>0.1316419679066984</v>
+      </c>
+      <c r="Y9">
+        <v>-0.3480600027429348</v>
+      </c>
+      <c r="Z9">
+        <v>0.6951239301308485</v>
+      </c>
+      <c r="AA9">
+        <v>-0.2274726835280962</v>
+      </c>
+      <c r="AB9">
+        <v>0.1229469165889224</v>
+      </c>
+      <c r="AC9">
+        <v>-0.3504196001170186</v>
+      </c>
+      <c r="AD9">
+        <v>1174</v>
+      </c>
+      <c r="AE9">
+        <v>41.52714185508196</v>
+      </c>
+      <c r="AF9">
+        <v>1215.527141855082</v>
+      </c>
+      <c r="AG9">
+        <v>11.32714185508189</v>
+      </c>
+      <c r="AH9">
+        <v>0.1311711376894765</v>
+      </c>
+      <c r="AI9">
+        <v>0.118330260034492</v>
+      </c>
+      <c r="AJ9">
+        <v>0.001404912089694456</v>
+      </c>
+      <c r="AK9">
+        <v>0.001249115906502903</v>
+      </c>
+      <c r="AL9">
+        <v>50.1</v>
+      </c>
+      <c r="AM9">
+        <v>50.1</v>
+      </c>
+      <c r="AN9">
+        <v>-0.8345299193903809</v>
+      </c>
+      <c r="AO9">
+        <v>-29.46506986027944</v>
+      </c>
+      <c r="AP9">
+        <v>-0.008051821788113202</v>
+      </c>
+      <c r="AQ9">
+        <v>-29.46506986027944</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SiriusPoint Ltd. (NYSE:SPNT)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Reinsurance</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.148</v>
+      </c>
+      <c r="G10">
+        <v>0.003257877885749593</v>
+      </c>
+      <c r="H10">
+        <v>0.003257877885749593</v>
+      </c>
+      <c r="I10">
+        <v>-0.3858133289988603</v>
+      </c>
+      <c r="J10">
+        <v>-0.3858133289988603</v>
+      </c>
+      <c r="K10">
+        <v>-500.5</v>
+      </c>
+      <c r="L10">
+        <v>-0.2811323934168399</v>
+      </c>
+      <c r="M10">
+        <v>12.1</v>
+      </c>
+      <c r="N10">
+        <v>0.01279610829103215</v>
+      </c>
+      <c r="O10">
+        <v>-0.02417582417582418</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
         <v>0</v>
       </c>
-      <c r="H9">
+      <c r="S10">
+        <v>12.1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>647.3</v>
+      </c>
+      <c r="V10">
+        <v>0.6845389170896784</v>
+      </c>
+      <c r="W10">
+        <v>-0.2052912223133716</v>
+      </c>
+      <c r="X10">
+        <v>0.1883143918527734</v>
+      </c>
+      <c r="Y10">
+        <v>-0.393605614166145</v>
+      </c>
+      <c r="Z10">
+        <v>0.6377306693635156</v>
+      </c>
+      <c r="AA10">
+        <v>-0.2460449925518094</v>
+      </c>
+      <c r="AB10">
+        <v>0.1334417017938161</v>
+      </c>
+      <c r="AC10">
+        <v>-0.3794866943456255</v>
+      </c>
+      <c r="AD10">
+        <v>779.3</v>
+      </c>
+      <c r="AE10">
+        <v>27.81734808335442</v>
+      </c>
+      <c r="AF10">
+        <v>807.1173480833544</v>
+      </c>
+      <c r="AG10">
+        <v>159.8173480833544</v>
+      </c>
+      <c r="AH10">
+        <v>0.4604948704170469</v>
+      </c>
+      <c r="AI10">
+        <v>0.278324259350634</v>
+      </c>
+      <c r="AJ10">
+        <v>0.1445764790650846</v>
+      </c>
+      <c r="AK10">
+        <v>0.07094740179433291</v>
+      </c>
+      <c r="AL10">
+        <v>37.7</v>
+      </c>
+      <c r="AM10">
+        <v>37.7</v>
+      </c>
+      <c r="AN10">
+        <v>-1.166966157532195</v>
+      </c>
+      <c r="AO10">
+        <v>-18.3474801061008</v>
+      </c>
+      <c r="AP10">
+        <v>-0.2393191795198479</v>
+      </c>
+      <c r="AQ10">
+        <v>-18.3474801061008</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>R&amp;Q Insurance Holdings Ltd. (AIM:RQIH)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Reinsurance</t>
+        </is>
+      </c>
+      <c r="K11">
+        <v>-213</v>
+      </c>
+      <c r="M11">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="N11">
+        <v>0.02992069214131219</v>
+      </c>
+      <c r="O11">
+        <v>-0.03896713615023475</v>
+      </c>
+      <c r="P11">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Q11">
+        <v>0.02992069214131219</v>
+      </c>
+      <c r="R11">
+        <v>-0.03896713615023475</v>
+      </c>
+      <c r="S11">
         <v>0</v>
       </c>
-      <c r="I9">
-        <v>-0.1896804212767448</v>
-      </c>
-      <c r="J9">
-        <v>-0.1896804212767448</v>
-      </c>
-      <c r="K9">
-        <v>-6.46</v>
-      </c>
-      <c r="L9">
-        <v>-0.2266666666666667</v>
-      </c>
-      <c r="M9">
-        <v>-0</v>
-      </c>
-      <c r="N9">
-        <v>-0</v>
-      </c>
-      <c r="O9">
+      <c r="T11">
         <v>0</v>
       </c>
-      <c r="P9">
-        <v>-0</v>
-      </c>
-      <c r="Q9">
-        <v>-0</v>
-      </c>
-      <c r="R9">
+      <c r="U11">
+        <v>375.8</v>
+      </c>
+      <c r="V11">
+        <v>1.354722422494593</v>
+      </c>
+      <c r="W11">
+        <v>-0.4295220810647308</v>
+      </c>
+      <c r="X11">
+        <v>0.2331607478552263</v>
+      </c>
+      <c r="Y11">
+        <v>-0.6626828289199571</v>
+      </c>
+      <c r="Z11">
         <v>0</v>
       </c>
-      <c r="S9">
+      <c r="AA11">
+        <v>-0.4065609452736318</v>
+      </c>
+      <c r="AB11">
+        <v>0.13499739029806</v>
+      </c>
+      <c r="AC11">
+        <v>-0.5415583355716918</v>
+      </c>
+      <c r="AD11">
+        <v>391</v>
+      </c>
+      <c r="AE11">
         <v>0</v>
       </c>
-      <c r="U9">
-        <v>37.5</v>
-      </c>
-      <c r="V9">
-        <v>4.290617848970252</v>
-      </c>
-      <c r="W9">
-        <v>-0.1422907488986784</v>
-      </c>
-      <c r="X9">
-        <v>0.2330278171269527</v>
-      </c>
-      <c r="Y9">
-        <v>-0.3753185660256311</v>
-      </c>
-      <c r="Z9">
-        <v>2.596938702866823</v>
-      </c>
-      <c r="AA9">
-        <v>-0.4925884271896621</v>
-      </c>
-      <c r="AB9">
-        <v>0.1005582618782724</v>
-      </c>
-      <c r="AC9">
-        <v>-0.5931466890679344</v>
-      </c>
-      <c r="AD9">
-        <v>16.5</v>
-      </c>
-      <c r="AE9">
-        <v>2.074460031936129</v>
-      </c>
-      <c r="AF9">
-        <v>18.57446003193613</v>
-      </c>
-      <c r="AG9">
-        <v>-18.92553996806387</v>
-      </c>
-      <c r="AH9">
-        <v>0.6800229625706979</v>
-      </c>
-      <c r="AI9">
-        <v>0.290341802379633</v>
-      </c>
-      <c r="AJ9">
-        <v>1.858079201240555</v>
-      </c>
-      <c r="AK9">
-        <v>-0.7148602821449052</v>
-      </c>
-      <c r="AL9">
-        <v>1.8</v>
-      </c>
-      <c r="AM9">
-        <v>1.8</v>
-      </c>
-      <c r="AN9">
-        <v>51.72413793103448</v>
-      </c>
-      <c r="AO9">
-        <v>-2.95</v>
-      </c>
-      <c r="AP9">
-        <v>-59.32771149863283</v>
-      </c>
-      <c r="AQ9">
-        <v>-2.95</v>
+      <c r="AF11">
+        <v>391</v>
+      </c>
+      <c r="AG11">
+        <v>15.19999999999999</v>
+      </c>
+      <c r="AH11">
+        <v>0.5849790544584081</v>
+      </c>
+      <c r="AI11">
+        <v>0.5874399038461539</v>
+      </c>
+      <c r="AJ11">
+        <v>0.05194805194805192</v>
+      </c>
+      <c r="AK11">
+        <v>0.05244996549344371</v>
+      </c>
+      <c r="AL11">
+        <v>27.4</v>
+      </c>
+      <c r="AM11">
+        <v>27.4</v>
+      </c>
+      <c r="AN11">
+        <v>-1.570912012856569</v>
+      </c>
+      <c r="AO11">
+        <v>-9.543795620437956</v>
+      </c>
+      <c r="AP11">
+        <v>-0.06106870229007629</v>
+      </c>
+      <c r="AQ11">
+        <v>-9.543795620437956</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bermuda/bermuda_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_reinsurance.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.134</v>
+        <v>0.138</v>
       </c>
       <c r="E2">
-        <v>0.144</v>
+        <v>0.4555</v>
       </c>
       <c r="F2">
-        <v>0.916</v>
+        <v>0.5415</v>
       </c>
       <c r="G2">
-        <v>0.0114998241449046</v>
+        <v>-0.02311767538930808</v>
       </c>
       <c r="H2">
-        <v>0.0114998241449046</v>
+        <v>-0.02311767538930808</v>
       </c>
       <c r="I2">
-        <v>-0.09328495135704365</v>
+        <v>0.2056558725745287</v>
       </c>
       <c r="J2">
-        <v>-0.08963413474295462</v>
+        <v>0.1988345395009495</v>
       </c>
       <c r="K2">
-        <v>-2373.22</v>
+        <v>4802.89</v>
       </c>
       <c r="L2">
-        <v>-0.08694642281426772</v>
+        <v>0.1427876182491691</v>
       </c>
       <c r="M2">
-        <v>1256.595</v>
+        <v>862.0549999999999</v>
       </c>
       <c r="N2">
-        <v>0.04388917781334906</v>
+        <v>0.02274338419488412</v>
       </c>
       <c r="O2">
-        <v>-0.529489470002781</v>
+        <v>0.1794867257005678</v>
       </c>
       <c r="P2">
-        <v>409.235</v>
+        <v>445.875</v>
       </c>
       <c r="Q2">
-        <v>0.01429337828214015</v>
+        <v>0.01176341002359937</v>
       </c>
       <c r="R2">
-        <v>-0.1724387119609644</v>
+        <v>0.09283473075585741</v>
       </c>
       <c r="S2">
-        <v>847.36</v>
+        <v>416.18</v>
       </c>
       <c r="T2">
-        <v>0.674330233687067</v>
+        <v>0.48277662098126</v>
       </c>
       <c r="U2">
-        <v>8121.4</v>
+        <v>8101.3</v>
       </c>
       <c r="V2">
-        <v>0.2836566822988576</v>
+        <v>0.2137345974189753</v>
       </c>
       <c r="W2">
-        <v>-0.0874495483374976</v>
+        <v>0.1663461538461539</v>
       </c>
       <c r="X2">
-        <v>0.1883143918527734</v>
+        <v>0.1268170066065673</v>
       </c>
       <c r="Y2">
-        <v>-0.275763940190271</v>
+        <v>0.03952914723958659</v>
       </c>
       <c r="Z2">
-        <v>0.9261888044736549</v>
+        <v>1.269264866676389</v>
       </c>
       <c r="AA2">
-        <v>-0.09871386171265252</v>
+        <v>0.1721432195215421</v>
       </c>
       <c r="AB2">
-        <v>0.1334417017938161</v>
+        <v>0.10823607317781</v>
       </c>
       <c r="AC2">
-        <v>-0.218236818261605</v>
+        <v>0.0639071463437321</v>
       </c>
       <c r="AD2">
-        <v>13565.9</v>
+        <v>11280.2</v>
       </c>
       <c r="AE2">
-        <v>222.3720214038894</v>
+        <v>239.5883827980423</v>
       </c>
       <c r="AF2">
-        <v>13788.27202140389</v>
+        <v>11519.78838279804</v>
       </c>
       <c r="AG2">
-        <v>5666.872021403889</v>
+        <v>3418.488382798042</v>
       </c>
       <c r="AH2">
-        <v>0.3250466618155791</v>
+        <v>0.2330839793454249</v>
       </c>
       <c r="AI2">
-        <v>0.3526351673407589</v>
+        <v>0.2235099257933192</v>
       </c>
       <c r="AJ2">
-        <v>0.1652247447783468</v>
+        <v>0.0827279707532803</v>
       </c>
       <c r="AK2">
-        <v>0.1829246348167443</v>
+        <v>0.07869613544081118</v>
       </c>
       <c r="AL2">
-        <v>444.9</v>
+        <v>700.24</v>
       </c>
       <c r="AM2">
-        <v>444.9</v>
+        <v>700.24</v>
       </c>
       <c r="AN2">
-        <v>-4.60449612029479</v>
+        <v>5.529097831926249</v>
       </c>
       <c r="AO2">
-        <v>-5.713526635198921</v>
+        <v>9.89350794013481</v>
       </c>
       <c r="AP2">
-        <v>-1.923432299866674</v>
+        <v>1.6756047504294</v>
       </c>
       <c r="AQ2">
-        <v>-5.713526635198921</v>
+        <v>9.89350794013481</v>
       </c>
     </row>
     <row r="3">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0124</v>
+        <v>0.194</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,16 +734,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.005744255078350416</v>
+        <v>0.1801982487444349</v>
       </c>
       <c r="J3">
-        <v>0.005744255078350416</v>
+        <v>0.1801982487444349</v>
       </c>
       <c r="K3">
-        <v>-1.76</v>
+        <v>5.19</v>
       </c>
       <c r="L3">
-        <v>-0.05365853658536586</v>
+        <v>0.1187643020594966</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,7 +752,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -761,70 +761,70 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>22.7</v>
+        <v>39</v>
       </c>
       <c r="V3">
-        <v>2.391991570073762</v>
+        <v>5.531914893617022</v>
       </c>
       <c r="W3">
-        <v>-0.04512820512820513</v>
+        <v>0.1663461538461539</v>
       </c>
       <c r="X3">
-        <v>0.2709565010563562</v>
+        <v>0.3010627106074093</v>
       </c>
       <c r="Y3">
-        <v>-0.3160847061845614</v>
+        <v>-0.1347165567612554</v>
       </c>
       <c r="AB3">
-        <v>0.201719857147425</v>
+        <v>0.1195306722807915</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AE3">
-        <v>1.322942167150532</v>
+        <v>1.536682649340969</v>
       </c>
       <c r="AF3">
-        <v>17.82294216715053</v>
+        <v>22.53668264934097</v>
       </c>
       <c r="AG3">
-        <v>-4.877057832849466</v>
+        <v>-16.46331735065903</v>
       </c>
       <c r="AH3">
-        <v>0.6525456707694535</v>
+        <v>0.7617171183550367</v>
       </c>
       <c r="AI3">
-        <v>0.3251000669174209</v>
+        <v>0.3798102900784811</v>
       </c>
       <c r="AJ3">
-        <v>-1.057255360273047</v>
+        <v>1.748938948659414</v>
       </c>
       <c r="AK3">
-        <v>-0.1518247552628236</v>
+        <v>-0.8095379976435118</v>
       </c>
       <c r="AL3">
-        <v>1.8</v>
+        <v>2.64</v>
       </c>
       <c r="AM3">
-        <v>1.8</v>
+        <v>2.64</v>
       </c>
       <c r="AN3">
-        <v>44.4743935309973</v>
+        <v>59.65909090909091</v>
       </c>
       <c r="AO3">
-        <v>0.04555555555555556</v>
+        <v>2.965909090909091</v>
       </c>
       <c r="AP3">
-        <v>-13.14570844433818</v>
+        <v>-46.77078792800862</v>
       </c>
       <c r="AQ3">
-        <v>0.04555555555555556</v>
+        <v>2.965909090909091</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brookfield Reinsurance Ltd. (NYSE:BNRE)</t>
+          <t>RenaissanceRe Holdings Ltd. (NYSE:RNR)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -843,116 +843,125 @@
           <t>Reinsurance</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.315</v>
+      </c>
+      <c r="E4">
+        <v>0.363</v>
+      </c>
+      <c r="F4">
+        <v>0.706</v>
+      </c>
       <c r="G4">
-        <v>0.002595437616387337</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.002595437616387337</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.04667132216014898</v>
+        <v>0.3124561672862792</v>
       </c>
       <c r="J4">
-        <v>0.03951079054105763</v>
+        <v>0.3059425516700775</v>
       </c>
       <c r="K4">
-        <v>307</v>
+        <v>1432.5</v>
       </c>
       <c r="L4">
-        <v>0.03573091247672253</v>
+        <v>0.1797342567847329</v>
       </c>
       <c r="M4">
-        <v>32.13500000000001</v>
+        <v>91.3</v>
       </c>
       <c r="N4">
-        <v>0.02246417336595596</v>
+        <v>0.008873640525226215</v>
       </c>
       <c r="O4">
-        <v>0.1046742671009772</v>
+        <v>0.06373472949389179</v>
       </c>
       <c r="P4">
-        <v>25.13500000000001</v>
+        <v>71.3</v>
       </c>
       <c r="Q4">
-        <v>0.01757077944774555</v>
+        <v>0.00692979813196746</v>
       </c>
       <c r="R4">
-        <v>0.08187296416938113</v>
+        <v>0.04977312390924956</v>
       </c>
       <c r="S4">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T4">
-        <v>0.2178310253617551</v>
+        <v>0.2190580503833516</v>
       </c>
       <c r="U4">
-        <v>3153</v>
+        <v>1195.9</v>
       </c>
       <c r="V4">
-        <v>2.204124432016777</v>
+        <v>0.1162320559049072</v>
       </c>
       <c r="W4">
-        <v>0.2402190923317684</v>
+        <v>0.346692804762942</v>
       </c>
       <c r="X4">
-        <v>0.4554265980511781</v>
+        <v>0.1131850041034975</v>
       </c>
       <c r="Y4">
-        <v>-0.2152075057194097</v>
+        <v>0.2335078006594445</v>
       </c>
       <c r="Z4">
-        <v>9.853211009174313</v>
+        <v>1.620049166146673</v>
       </c>
       <c r="AA4">
-        <v>0.3893081563403293</v>
+        <v>0.4956419757218946</v>
       </c>
       <c r="AB4">
-        <v>0.1346675300480364</v>
+        <v>0.1046939261110405</v>
       </c>
       <c r="AC4">
-        <v>0.2546406262922929</v>
+        <v>0.390948049610854</v>
       </c>
       <c r="AD4">
-        <v>5958</v>
+        <v>1890</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>67.96550555813053</v>
       </c>
       <c r="AF4">
-        <v>5958</v>
+        <v>1957.965505558131</v>
       </c>
       <c r="AG4">
-        <v>2805</v>
+        <v>762.0655055581306</v>
       </c>
       <c r="AH4">
-        <v>0.8063883061514516</v>
+        <v>0.159874827127768</v>
       </c>
       <c r="AI4">
-        <v>0.8998640688717716</v>
+        <v>0.1287384325177039</v>
       </c>
       <c r="AJ4">
-        <v>0.6622594734978161</v>
+        <v>0.06895917874097485</v>
       </c>
       <c r="AK4">
-        <v>0.8088235294117647</v>
+        <v>0.05438288599624851</v>
       </c>
       <c r="AL4">
-        <v>122</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AM4">
-        <v>122</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AN4">
-        <v>14.31867339581831</v>
+        <v>266.1971830985916</v>
       </c>
       <c r="AO4">
-        <v>3.286885245901639</v>
+        <v>38.65015479876162</v>
       </c>
       <c r="AP4">
-        <v>6.741167988464311</v>
+        <v>107.3331697969198</v>
       </c>
       <c r="AQ4">
-        <v>3.286885245901639</v>
+        <v>38.65015479876162</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Everest Re Group, Ltd. (NYSE:RE)</t>
+          <t>Brookfield Reinsurance Ltd. (NYSE:BNRE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -971,125 +980,116 @@
           <t>Reinsurance</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.134</v>
-      </c>
-      <c r="E5">
-        <v>0.144</v>
-      </c>
-      <c r="F5">
-        <v>0.167</v>
-      </c>
       <c r="G5">
+        <v>0.1112682030255903</v>
+      </c>
+      <c r="H5">
+        <v>0.1112682030255903</v>
+      </c>
+      <c r="I5">
+        <v>0.1415241057542768</v>
+      </c>
+      <c r="J5">
+        <v>0.1349841748044489</v>
+      </c>
+      <c r="K5">
+        <v>513</v>
+      </c>
+      <c r="L5">
+        <v>0.07252933691502898</v>
+      </c>
+      <c r="M5">
+        <v>43.375</v>
+      </c>
+      <c r="N5">
+        <v>0.009547865900636159</v>
+      </c>
+      <c r="O5">
+        <v>0.08455165692007797</v>
+      </c>
+      <c r="P5">
+        <v>39.375</v>
+      </c>
+      <c r="Q5">
+        <v>0.008667371062537146</v>
+      </c>
+      <c r="R5">
+        <v>0.07675438596491228</v>
+      </c>
+      <c r="S5">
+        <v>4</v>
+      </c>
+      <c r="T5">
+        <v>0.09221902017291066</v>
+      </c>
+      <c r="U5">
+        <v>3448</v>
+      </c>
+      <c r="V5">
+        <v>0.7589865504413481</v>
+      </c>
+      <c r="W5">
+        <v>0.783206106870229</v>
+      </c>
+      <c r="X5">
+        <v>0.1436478329097824</v>
+      </c>
+      <c r="Y5">
+        <v>0.6395582739604466</v>
+      </c>
+      <c r="Z5">
+        <v>2.153775883069427</v>
+      </c>
+      <c r="AA5">
+        <v>0.2907256602898499</v>
+      </c>
+      <c r="AB5">
+        <v>0.1098868067829585</v>
+      </c>
+      <c r="AC5">
+        <v>0.1808388535068913</v>
+      </c>
+      <c r="AD5">
+        <v>3079</v>
+      </c>
+      <c r="AE5">
         <v>0</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0.05712112050887563</v>
-      </c>
-      <c r="J5">
-        <v>0.05712112050887563</v>
-      </c>
-      <c r="K5">
-        <v>532.1</v>
-      </c>
-      <c r="L5">
-        <v>0.0443283681562198</v>
-      </c>
-      <c r="M5">
-        <v>357.9</v>
-      </c>
-      <c r="N5">
-        <v>0.0275855158699573</v>
-      </c>
-      <c r="O5">
-        <v>0.6726179289607216</v>
-      </c>
-      <c r="P5">
-        <v>251.7</v>
-      </c>
-      <c r="Q5">
-        <v>0.01940004007954247</v>
-      </c>
-      <c r="R5">
-        <v>0.4730313850779928</v>
-      </c>
-      <c r="S5">
-        <v>106.2</v>
-      </c>
-      <c r="T5">
-        <v>0.2967309304274937</v>
-      </c>
-      <c r="U5">
-        <v>1679</v>
-      </c>
-      <c r="V5">
-        <v>0.1294106765735074</v>
-      </c>
-      <c r="W5">
-        <v>0.05332411360311066</v>
-      </c>
-      <c r="X5">
-        <v>0.1395809498475814</v>
-      </c>
-      <c r="Y5">
-        <v>-0.08625683624447075</v>
-      </c>
-      <c r="Z5">
-        <v>1.093940924793924</v>
-      </c>
-      <c r="AA5">
-        <v>0.06248713139474459</v>
-      </c>
-      <c r="AB5">
-        <v>0.1232273068909808</v>
-      </c>
-      <c r="AC5">
-        <v>-0.06074017549623621</v>
-      </c>
-      <c r="AD5">
-        <v>3084</v>
-      </c>
-      <c r="AE5">
-        <v>151.7045892983024</v>
-      </c>
       <c r="AF5">
-        <v>3235.704589298302</v>
+        <v>3079</v>
       </c>
       <c r="AG5">
-        <v>1556.704589298302</v>
+        <v>-369</v>
       </c>
       <c r="AH5">
-        <v>0.199612809037414</v>
+        <v>0.4039675146616986</v>
       </c>
       <c r="AI5">
-        <v>0.2972707768734123</v>
+        <v>0.3114820435002529</v>
       </c>
       <c r="AJ5">
-        <v>0.1071306042739267</v>
+        <v>-0.08840652627039461</v>
       </c>
       <c r="AK5">
-        <v>0.169102166401036</v>
+        <v>-0.05732484076433121</v>
       </c>
       <c r="AL5">
-        <v>97.09999999999999</v>
+        <v>317</v>
       </c>
       <c r="AM5">
-        <v>97.09999999999999</v>
+        <v>317</v>
       </c>
       <c r="AN5">
-        <v>147.5598086124402</v>
+        <v>2.957732949087416</v>
       </c>
       <c r="AO5">
-        <v>7.158599382080331</v>
+        <v>3.157728706624606</v>
       </c>
       <c r="AP5">
-        <v>74.48347317216758</v>
+        <v>-0.3544668587896254</v>
       </c>
       <c r="AQ5">
-        <v>7.158599382080331</v>
+        <v>3.157728706624606</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maiden Holdings, Ltd. (NasdaqCM:MHLD)</t>
+          <t>Everest Group, Ltd. (NYSE:EG)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,118 +1109,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.4970000000000001</v>
+        <v>0.138</v>
+      </c>
+      <c r="E6">
+        <v>0.161</v>
+      </c>
+      <c r="F6">
+        <v>0.377</v>
       </c>
       <c r="G6">
-        <v>0.4625850340136055</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0.4625850340136055</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.02816326530612245</v>
+        <v>0.1794017634923285</v>
       </c>
       <c r="J6">
-        <v>0.02256438114814271</v>
+        <v>0.1617544879814505</v>
       </c>
       <c r="K6">
-        <v>3.34</v>
+        <v>2209</v>
       </c>
       <c r="L6">
-        <v>0.0454421768707483</v>
+        <v>0.1560700584291256</v>
       </c>
       <c r="M6">
-        <v>1.06</v>
+        <v>300</v>
       </c>
       <c r="N6">
-        <v>0.00576400217509516</v>
+        <v>0.01955416503715291</v>
       </c>
       <c r="O6">
-        <v>0.3173652694610778</v>
+        <v>0.1358080579447714</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>276</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.01798983183418068</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.1249434133091897</v>
       </c>
       <c r="S6">
-        <v>1.06</v>
+        <v>24</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="U6">
-        <v>24.4</v>
+        <v>1765</v>
       </c>
       <c r="V6">
-        <v>0.1326808047852093</v>
+        <v>0.115043670968583</v>
       </c>
       <c r="W6">
-        <v>0.0154772937905468</v>
+        <v>0.2887959210354294</v>
       </c>
       <c r="X6">
-        <v>0.2315333633803699</v>
+        <v>0.11444268907381</v>
       </c>
       <c r="Y6">
-        <v>-0.2160560695898231</v>
+        <v>0.1743532319616194</v>
       </c>
       <c r="Z6">
-        <v>0.1206500328299409</v>
+        <v>1.53891452985788</v>
       </c>
       <c r="AA6">
-        <v>0.002722393326310717</v>
+        <v>0.2489263318243759</v>
       </c>
       <c r="AB6">
-        <v>0.1349043362361488</v>
+        <v>0.1039807171573485</v>
       </c>
       <c r="AC6">
-        <v>-0.1321819429098381</v>
+        <v>0.1449456146670274</v>
       </c>
       <c r="AD6">
-        <v>255.5</v>
+        <v>3085</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>143.3268985296575</v>
       </c>
       <c r="AF6">
-        <v>255.5</v>
+        <v>3228.326898529658</v>
       </c>
       <c r="AG6">
-        <v>231.1</v>
+        <v>1463.326898529658</v>
       </c>
       <c r="AH6">
-        <v>0.581474738279472</v>
+        <v>0.1738432993759128</v>
       </c>
       <c r="AI6">
-        <v>0.4383256133127466</v>
+        <v>0.2233467473921635</v>
       </c>
       <c r="AJ6">
-        <v>0.5568674698795181</v>
+        <v>0.08707518201610753</v>
       </c>
       <c r="AK6">
-        <v>0.4137869292748433</v>
+        <v>0.1153195051424845</v>
       </c>
       <c r="AL6">
-        <v>19.3</v>
+        <v>126</v>
       </c>
       <c r="AM6">
-        <v>19.3</v>
+        <v>126</v>
       </c>
       <c r="AN6">
-        <v>52.35655737704918</v>
+        <v>146.9047619047619</v>
       </c>
       <c r="AO6">
-        <v>0.1072538860103627</v>
+        <v>20.21349206349207</v>
       </c>
       <c r="AP6">
-        <v>47.35655737704918</v>
+        <v>69.68223326331703</v>
       </c>
       <c r="AQ6">
-        <v>0.1072538860103627</v>
+        <v>20.21349206349207</v>
       </c>
     </row>
     <row r="7">
@@ -1231,7 +1237,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Conduit Holdings Limited (LSE:CRE)</t>
+          <t>SiriusPoint Ltd. (NYSE:SPNT)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1239,110 +1245,122 @@
           <t>Reinsurance</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.34</v>
+      </c>
+      <c r="E7">
+        <v>0.569</v>
+      </c>
       <c r="G7">
-        <v>-0.1351619299405155</v>
+        <v>-0.147141925668333</v>
       </c>
       <c r="H7">
-        <v>-0.1351619299405155</v>
+        <v>-0.147141925668333</v>
       </c>
       <c r="I7">
-        <v>-0.2967614011896893</v>
+        <v>0.161359175826928</v>
       </c>
       <c r="J7">
-        <v>-0.2967614011896893</v>
+        <v>0.1398833142960059</v>
       </c>
       <c r="K7">
-        <v>-91</v>
+        <v>234.7</v>
       </c>
       <c r="L7">
-        <v>-0.3007270323859881</v>
+        <v>0.08501774976454393</v>
       </c>
       <c r="M7">
-        <v>62.6</v>
+        <v>9.4</v>
       </c>
       <c r="N7">
-        <v>0.07580527972874788</v>
+        <v>0.004835639693399866</v>
       </c>
       <c r="O7">
-        <v>-0.6879120879120879</v>
+        <v>0.04005112910097998</v>
       </c>
       <c r="P7">
-        <v>59.4</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.07193024945507387</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0.6527472527472528</v>
+        <v>-0</v>
       </c>
       <c r="S7">
-        <v>3.200000000000003</v>
+        <v>9.4</v>
       </c>
       <c r="T7">
-        <v>0.05111821086261985</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>92</v>
+        <v>703.5</v>
       </c>
       <c r="V7">
-        <v>0.1114071203681279</v>
+        <v>0.3619013323730644</v>
       </c>
       <c r="W7">
-        <v>-0.0874495483374976</v>
+        <v>0.1245423189174847</v>
       </c>
       <c r="X7">
-        <v>0.1197177482092605</v>
+        <v>0.1268170066065673</v>
       </c>
       <c r="Y7">
-        <v>-0.2071672965467581</v>
+        <v>-0.002274687689082538</v>
       </c>
       <c r="Z7">
-        <v>0.3326371331208091</v>
+        <v>1.230620109252425</v>
       </c>
       <c r="AA7">
-        <v>-0.09871386171265252</v>
+        <v>0.1721432195215421</v>
       </c>
       <c r="AB7">
-        <v>0.1195229565489525</v>
+        <v>0.10823607317781</v>
       </c>
       <c r="AC7">
-        <v>-0.218236818261605</v>
+        <v>0.0639071463437321</v>
       </c>
       <c r="AD7">
-        <v>2.6</v>
+        <v>767.2</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>26.75929606091326</v>
       </c>
       <c r="AF7">
-        <v>2.6</v>
+        <v>793.9592960609133</v>
       </c>
       <c r="AG7">
-        <v>-89.40000000000001</v>
+        <v>90.45929606091329</v>
       </c>
       <c r="AH7">
-        <v>0.003138580395943989</v>
+        <v>0.2899927316218258</v>
       </c>
       <c r="AI7">
-        <v>0.002920035938903864</v>
+        <v>0.2595181602511277</v>
       </c>
       <c r="AJ7">
-        <v>-0.121401412275937</v>
+        <v>0.04446574222954013</v>
       </c>
       <c r="AK7">
-        <v>-0.1119739478957916</v>
+        <v>0.03839758011531702</v>
       </c>
       <c r="AL7">
-        <v>0.5</v>
+        <v>54.8</v>
       </c>
       <c r="AM7">
-        <v>0.5</v>
+        <v>54.8</v>
+      </c>
+      <c r="AN7">
+        <v>1.643178410794603</v>
       </c>
       <c r="AO7">
-        <v>-179.6</v>
+        <v>8.058394160583942</v>
+      </c>
+      <c r="AP7">
+        <v>0.1937444764637252</v>
       </c>
       <c r="AQ7">
-        <v>-179.6</v>
+        <v>8.058394160583942</v>
       </c>
     </row>
     <row r="8">
@@ -1361,17 +1379,38 @@
           <t>Reinsurance</t>
         </is>
       </c>
+      <c r="D8">
+        <v>-0.00843</v>
+      </c>
+      <c r="E8">
+        <v>0.5479999999999999</v>
+      </c>
+      <c r="G8">
+        <v>-0.8397790055248618</v>
+      </c>
+      <c r="H8">
+        <v>-0.8397790055248618</v>
+      </c>
+      <c r="I8">
+        <v>0.8033149171270718</v>
+      </c>
+      <c r="J8">
+        <v>0.8033149171270718</v>
+      </c>
       <c r="K8">
-        <v>-1111</v>
+        <v>746</v>
+      </c>
+      <c r="L8">
+        <v>0.8243093922651934</v>
       </c>
       <c r="M8">
-        <v>215</v>
+        <v>340</v>
       </c>
       <c r="N8">
-        <v>0.05466564963132469</v>
+        <v>0.07464816563110634</v>
       </c>
       <c r="O8">
-        <v>-0.1935193519351935</v>
+        <v>0.4557640750670242</v>
       </c>
       <c r="P8">
         <v>-0</v>
@@ -1380,82 +1419,82 @@
         <v>-0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S8">
-        <v>215</v>
+        <v>340</v>
       </c>
       <c r="T8">
         <v>1</v>
       </c>
       <c r="U8">
-        <v>923</v>
+        <v>497</v>
       </c>
       <c r="V8">
-        <v>0.2346809051614544</v>
+        <v>0.1091180538784113</v>
       </c>
       <c r="W8">
-        <v>-0.185444833917543</v>
+        <v>0.1878147029204431</v>
       </c>
       <c r="X8">
-        <v>0.1585343390611268</v>
+        <v>0.1264149310702275</v>
       </c>
       <c r="Y8">
-        <v>-0.3439791729786699</v>
+        <v>0.06139977185021564</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>0.1794922649742166</v>
       </c>
       <c r="AA8">
-        <v>-0.1812947778694225</v>
+        <v>0.1441888139627132</v>
       </c>
       <c r="AB8">
-        <v>0.1293686485451029</v>
+        <v>0.1077752683169365</v>
       </c>
       <c r="AC8">
-        <v>-0.3106634264145254</v>
+        <v>0.0364135456457767</v>
       </c>
       <c r="AD8">
-        <v>1905</v>
+        <v>1831</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1905</v>
+        <v>1831</v>
       </c>
       <c r="AG8">
-        <v>982</v>
+        <v>1334</v>
       </c>
       <c r="AH8">
-        <v>0.3263103802672148</v>
+        <v>0.2867344222246582</v>
       </c>
       <c r="AI8">
-        <v>0.3058275806710548</v>
+        <v>0.2653238661063614</v>
       </c>
       <c r="AJ8">
-        <v>0.1997965412004069</v>
+        <v>0.2265355681219964</v>
       </c>
       <c r="AK8">
-        <v>0.185073501696193</v>
+        <v>0.2083073079325422</v>
       </c>
       <c r="AL8">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AM8">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AN8">
-        <v>-1.788732394366197</v>
+        <v>2.481029810298103</v>
       </c>
       <c r="AO8">
-        <v>-12.59550561797753</v>
+        <v>8.552941176470588</v>
       </c>
       <c r="AP8">
-        <v>-0.9220657276995305</v>
+        <v>1.807588075880759</v>
       </c>
       <c r="AQ8">
-        <v>-12.59550561797753</v>
+        <v>8.552941176470588</v>
       </c>
     </row>
     <row r="9">
@@ -1466,7 +1505,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RenaissanceRe Holdings Ltd. (NYSE:RNR)</t>
+          <t>Conduit Holdings Limited (LSE:CRE)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1474,122 +1513,116 @@
           <t>Reinsurance</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.181</v>
-      </c>
-      <c r="F9">
-        <v>1.665</v>
-      </c>
       <c r="G9">
-        <v>-0.001465501951046471</v>
+        <v>-0.1540465439388677</v>
       </c>
       <c r="H9">
-        <v>-0.001465501951046471</v>
+        <v>-0.1540465439388677</v>
       </c>
       <c r="I9">
-        <v>-0.3272404727676074</v>
+        <v>0.05175408127822161</v>
       </c>
       <c r="J9">
-        <v>-0.3272404727676074</v>
+        <v>0.05175408127822161</v>
       </c>
       <c r="K9">
-        <v>-1298.4</v>
+        <v>28.3</v>
       </c>
       <c r="L9">
-        <v>-0.287868038311458</v>
+        <v>0.049149010072942</v>
       </c>
       <c r="M9">
-        <v>567.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="N9">
-        <v>0.07048638712241653</v>
+        <v>0.080597331073925</v>
       </c>
       <c r="O9">
-        <v>-0.4370764017252002</v>
+        <v>2.689045936395759</v>
       </c>
       <c r="P9">
-        <v>64.7</v>
+        <v>59.2</v>
       </c>
       <c r="Q9">
-        <v>0.008036069157392687</v>
+        <v>0.0626985808091506</v>
       </c>
       <c r="R9">
-        <v>-0.0498305606900801</v>
+        <v>2.091872791519435</v>
       </c>
       <c r="S9">
-        <v>502.8</v>
+        <v>16.89999999999999</v>
       </c>
       <c r="T9">
-        <v>0.8859911894273128</v>
+        <v>0.2220762155059132</v>
       </c>
       <c r="U9">
-        <v>1204.2</v>
+        <v>118.1</v>
       </c>
       <c r="V9">
-        <v>0.1495677662957075</v>
+        <v>0.1250794323236602</v>
       </c>
       <c r="W9">
-        <v>-0.2164180348362364</v>
+        <v>0.031876548772246</v>
       </c>
       <c r="X9">
-        <v>0.1316419679066984</v>
+        <v>0.1014317047940883</v>
       </c>
       <c r="Y9">
-        <v>-0.3480600027429348</v>
+        <v>-0.06955515602184228</v>
       </c>
       <c r="Z9">
-        <v>0.6951239301308485</v>
+        <v>0.7211923847695391</v>
       </c>
       <c r="AA9">
-        <v>-0.2274726835280962</v>
+        <v>0.0373246492985972</v>
       </c>
       <c r="AB9">
-        <v>0.1229469165889224</v>
+        <v>0.1013270277091334</v>
       </c>
       <c r="AC9">
-        <v>-0.3504196001170186</v>
+        <v>-0.06400237841053619</v>
       </c>
       <c r="AD9">
-        <v>1174</v>
+        <v>2.1</v>
       </c>
       <c r="AE9">
-        <v>41.52714185508196</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1215.527141855082</v>
+        <v>2.1</v>
       </c>
       <c r="AG9">
-        <v>11.32714185508189</v>
+        <v>-116</v>
       </c>
       <c r="AH9">
-        <v>0.1311711376894765</v>
+        <v>0.002219169396597274</v>
       </c>
       <c r="AI9">
-        <v>0.118330260034492</v>
+        <v>0.002284595300261097</v>
       </c>
       <c r="AJ9">
-        <v>0.001404912089694456</v>
+        <v>-0.1400627867664815</v>
       </c>
       <c r="AK9">
-        <v>0.001249115906502903</v>
+        <v>-0.1448008987641992</v>
       </c>
       <c r="AL9">
-        <v>50.1</v>
+        <v>0.3</v>
       </c>
       <c r="AM9">
-        <v>50.1</v>
+        <v>0.3</v>
       </c>
       <c r="AN9">
-        <v>-0.8345299193903809</v>
+        <v>0.07094594594594594</v>
       </c>
       <c r="AO9">
-        <v>-29.46506986027944</v>
+        <v>99.33333333333334</v>
       </c>
       <c r="AP9">
-        <v>-0.008051821788113202</v>
+        <v>-3.918918918918919</v>
       </c>
       <c r="AQ9">
-        <v>-29.46506986027944</v>
+        <v>99.33333333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1600,7 +1633,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SiriusPoint Ltd. (NYSE:SPNT)</t>
+          <t>Maiden Holdings, Ltd. (NasdaqCM:MHLD)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1609,34 +1642,34 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.148</v>
+        <v>-0.491</v>
       </c>
       <c r="G10">
-        <v>0.003257877885749593</v>
+        <v>-0.6227951153324287</v>
       </c>
       <c r="H10">
-        <v>0.003257877885749593</v>
+        <v>-0.6227951153324287</v>
       </c>
       <c r="I10">
-        <v>-0.3858133289988603</v>
+        <v>-0.6648575305291723</v>
       </c>
       <c r="J10">
-        <v>-0.3858133289988603</v>
+        <v>-0.6648575305291723</v>
       </c>
       <c r="K10">
-        <v>-500.5</v>
+        <v>-68.8</v>
       </c>
       <c r="L10">
-        <v>-0.2811323934168399</v>
+        <v>-0.9335142469470827</v>
       </c>
       <c r="M10">
-        <v>12.1</v>
+        <v>1.88</v>
       </c>
       <c r="N10">
-        <v>0.01279610829103215</v>
+        <v>0.008131487889273356</v>
       </c>
       <c r="O10">
-        <v>-0.02417582417582418</v>
+        <v>-0.02732558139534884</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1648,79 +1681,73 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>12.1</v>
+        <v>1.88</v>
       </c>
       <c r="T10">
         <v>1</v>
       </c>
       <c r="U10">
-        <v>647.3</v>
+        <v>17.9</v>
       </c>
       <c r="V10">
-        <v>0.6845389170896784</v>
+        <v>0.07742214532871972</v>
       </c>
       <c r="W10">
-        <v>-0.2052912223133716</v>
+        <v>-0.3312469908521907</v>
       </c>
       <c r="X10">
-        <v>0.1883143918527734</v>
+        <v>0.1701103835244301</v>
       </c>
       <c r="Y10">
-        <v>-0.393605614166145</v>
+        <v>-0.5013573743766208</v>
       </c>
       <c r="Z10">
-        <v>0.6377306693635156</v>
+        <v>0.1319606087735005</v>
       </c>
       <c r="AA10">
-        <v>-0.2460449925518094</v>
+        <v>-0.08773500447627573</v>
       </c>
       <c r="AB10">
-        <v>0.1334417017938161</v>
+        <v>0.1124421905776576</v>
       </c>
       <c r="AC10">
-        <v>-0.3794866943456255</v>
+        <v>-0.2001771950539333</v>
       </c>
       <c r="AD10">
-        <v>779.3</v>
+        <v>254.6</v>
       </c>
       <c r="AE10">
-        <v>27.81734808335442</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>807.1173480833544</v>
+        <v>254.6</v>
       </c>
       <c r="AG10">
-        <v>159.8173480833544</v>
+        <v>236.7</v>
       </c>
       <c r="AH10">
-        <v>0.4604948704170469</v>
+        <v>0.5240839851790861</v>
       </c>
       <c r="AI10">
-        <v>0.278324259350634</v>
+        <v>0.4916956353804558</v>
       </c>
       <c r="AJ10">
-        <v>0.1445764790650846</v>
+        <v>0.5058773242145758</v>
       </c>
       <c r="AK10">
-        <v>0.07094740179433291</v>
+        <v>0.473494698939788</v>
       </c>
       <c r="AL10">
-        <v>37.7</v>
+        <v>18.2</v>
       </c>
       <c r="AM10">
-        <v>37.7</v>
-      </c>
-      <c r="AN10">
-        <v>-1.166966157532195</v>
+        <v>18.2</v>
       </c>
       <c r="AO10">
-        <v>-18.3474801061008</v>
-      </c>
-      <c r="AP10">
-        <v>-0.2393191795198479</v>
+        <v>-2.692307692307693</v>
       </c>
       <c r="AQ10">
-        <v>-18.3474801061008</v>
+        <v>-2.692307692307693</v>
       </c>
     </row>
     <row r="11">
@@ -1739,101 +1766,116 @@
           <t>Reinsurance</t>
         </is>
       </c>
+      <c r="D11">
+        <v>-0.184</v>
+      </c>
+      <c r="G11">
+        <v>-3.264851485148515</v>
+      </c>
+      <c r="H11">
+        <v>-3.264851485148515</v>
+      </c>
+      <c r="I11">
+        <v>-3.392326732673268</v>
+      </c>
+      <c r="J11">
+        <v>-3.392326732673268</v>
+      </c>
       <c r="K11">
-        <v>-213</v>
+        <v>-297</v>
+      </c>
+      <c r="L11">
+        <v>-3.675742574257426</v>
       </c>
       <c r="M11">
-        <v>8.300000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.02992069214131219</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>-0.03896713615023475</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>8.300000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.02992069214131219</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>-0.03896713615023475</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>375.8</v>
+        <v>316.9</v>
       </c>
       <c r="V11">
-        <v>1.354722422494593</v>
+        <v>6.507186858316221</v>
       </c>
       <c r="W11">
-        <v>-0.4295220810647308</v>
+        <v>-0.7475459350616662</v>
       </c>
       <c r="X11">
-        <v>0.2331607478552263</v>
+        <v>0.55080396423387</v>
       </c>
       <c r="Y11">
-        <v>-0.6626828289199571</v>
+        <v>-1.298349899295536</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>0.1765348481538125</v>
       </c>
       <c r="AA11">
-        <v>-0.4065609452736318</v>
+        <v>-0.5988638846405944</v>
       </c>
       <c r="AB11">
-        <v>0.13499739029806</v>
+        <v>0.1223135383097454</v>
       </c>
       <c r="AC11">
-        <v>-0.5415583355716918</v>
+        <v>-0.7211774229503398</v>
       </c>
       <c r="AD11">
-        <v>391</v>
+        <v>350.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>391</v>
+        <v>350.3</v>
       </c>
       <c r="AG11">
-        <v>15.19999999999999</v>
+        <v>33.40000000000003</v>
       </c>
       <c r="AH11">
-        <v>0.5849790544584081</v>
+        <v>0.8779448621553885</v>
       </c>
       <c r="AI11">
-        <v>0.5874399038461539</v>
+        <v>0.6541549953314659</v>
       </c>
       <c r="AJ11">
-        <v>0.05194805194805192</v>
+        <v>0.4068209500609016</v>
       </c>
       <c r="AK11">
-        <v>0.05244996549344371</v>
+        <v>0.1527904849039343</v>
       </c>
       <c r="AL11">
-        <v>27.4</v>
+        <v>31.7</v>
       </c>
       <c r="AM11">
-        <v>27.4</v>
+        <v>31.7</v>
       </c>
       <c r="AN11">
-        <v>-1.570912012856569</v>
+        <v>-1.327899924184989</v>
       </c>
       <c r="AO11">
-        <v>-9.543795620437956</v>
+        <v>-8.646687697160884</v>
       </c>
       <c r="AP11">
-        <v>-0.06106870229007629</v>
+        <v>-0.1266110689916605</v>
       </c>
       <c r="AQ11">
-        <v>-9.543795620437956</v>
+        <v>-8.646687697160884</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bermuda/bermuda_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_reinsurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.282</v>
+        <v>0.159</v>
       </c>
       <c r="E2">
-        <v>0.2615</v>
+        <v>0.42</v>
       </c>
       <c r="F2">
-        <v>0.355</v>
+        <v>0.181515</v>
       </c>
       <c r="G2">
-        <v>0.07536003035700077</v>
+        <v>0.05565749511895293</v>
       </c>
       <c r="H2">
-        <v>0.07536003035700077</v>
+        <v>0.05565749511895293</v>
       </c>
       <c r="I2">
-        <v>0.3518452357813557</v>
+        <v>0.2338050139135367</v>
       </c>
       <c r="J2">
-        <v>0.3518452357813557</v>
+        <v>0.2338050139135367</v>
       </c>
       <c r="K2">
-        <v>4988.2</v>
+        <v>9010.700000000001</v>
       </c>
       <c r="L2">
-        <v>0.3052959501557632</v>
+        <v>0.2036187540675393</v>
       </c>
       <c r="M2">
-        <v>648.6</v>
+        <v>1350.631</v>
       </c>
       <c r="N2">
-        <v>0.03194932244383254</v>
+        <v>0.02882754454976405</v>
       </c>
       <c r="O2">
-        <v>0.1300268633976184</v>
+        <v>0.1498919062891895</v>
       </c>
       <c r="P2">
-        <v>80.8</v>
+        <v>518.551</v>
       </c>
       <c r="Q2">
-        <v>0.003980119108019841</v>
+        <v>0.01106782833640328</v>
       </c>
       <c r="R2">
-        <v>0.01619822781764965</v>
+        <v>0.05754835917298323</v>
       </c>
       <c r="S2">
-        <v>567.8</v>
+        <v>832.08</v>
       </c>
       <c r="T2">
-        <v>0.8754239901325932</v>
+        <v>0.6160676009953866</v>
       </c>
       <c r="U2">
-        <v>2785.6</v>
+        <v>19381.8</v>
       </c>
       <c r="V2">
-        <v>0.1372155914269811</v>
+        <v>0.4136804967119937</v>
       </c>
       <c r="W2">
-        <v>0.2146585926080601</v>
+        <v>0.22930978083088</v>
       </c>
       <c r="X2">
-        <v>0.1193599822142334</v>
+        <v>0.1193298553146371</v>
       </c>
       <c r="Y2">
-        <v>0.0952986103938267</v>
+        <v>0.1099799255162429</v>
       </c>
       <c r="Z2">
-        <v>0.9650526203510691</v>
+        <v>1.188911532167118</v>
       </c>
       <c r="AA2">
-        <v>0.137517104756583</v>
+        <v>0.219959281614451</v>
       </c>
       <c r="AB2">
-        <v>0.1084531701758685</v>
+        <v>0.1084292222039559</v>
       </c>
       <c r="AC2">
-        <v>0.02906393458071449</v>
+        <v>0.113058024047731</v>
       </c>
       <c r="AD2">
-        <v>4445.4</v>
+        <v>17008</v>
       </c>
       <c r="AE2">
-        <v>123.1793854600344</v>
+        <v>258.8724014352116</v>
       </c>
       <c r="AF2">
-        <v>4568.579385460034</v>
+        <v>17266.87240143521</v>
       </c>
       <c r="AG2">
-        <v>1782.979385460034</v>
+        <v>-2114.927598564787</v>
       </c>
       <c r="AH2">
-        <v>0.1837022526547563</v>
+        <v>0.2692942783507354</v>
       </c>
       <c r="AI2">
-        <v>0.1451832316421462</v>
+        <v>0.2342485038536262</v>
       </c>
       <c r="AJ2">
-        <v>0.08073669278568613</v>
+        <v>-0.04727450317125851</v>
       </c>
       <c r="AK2">
-        <v>0.06216353289796309</v>
+        <v>-0.03892745578698138</v>
       </c>
       <c r="AL2">
-        <v>253.5</v>
+        <v>753.8</v>
       </c>
       <c r="AM2">
-        <v>253.5</v>
+        <v>753.8</v>
       </c>
       <c r="AN2">
-        <v>4.172909039707124</v>
+        <v>5.460731567221612</v>
       </c>
       <c r="AO2">
-        <v>22.68994082840237</v>
+        <v>13.73388166622446</v>
       </c>
       <c r="AP2">
-        <v>1.673687586088458</v>
+        <v>-0.6790364475465035</v>
       </c>
       <c r="AQ2">
-        <v>22.68994082840237</v>
+        <v>13.73388166622446</v>
       </c>
     </row>
     <row r="3">
@@ -785,10 +785,10 @@
         <v>0.5330769455736554</v>
       </c>
       <c r="X3">
-        <v>0.1135518146701345</v>
+        <v>0.1135240665378403</v>
       </c>
       <c r="Y3">
-        <v>0.4195251309035209</v>
+        <v>0.4195528790358151</v>
       </c>
       <c r="Z3">
         <v>1.510146395511916</v>
@@ -797,10 +797,10 @@
         <v>0.5634117953701668</v>
       </c>
       <c r="AB3">
-        <v>0.1067219246526203</v>
+        <v>0.1066979766807077</v>
       </c>
       <c r="AC3">
-        <v>0.4566898707175466</v>
+        <v>0.4567138186894592</v>
       </c>
       <c r="AD3">
         <v>1951.9</v>
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SiriusPoint Ltd. (NYSE:SPNT)</t>
+          <t>Conduit Holdings Limited (LSE:CRE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -861,119 +861,116 @@
           <t>Reinsurance</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.318</v>
-      </c>
       <c r="G4">
-        <v>0.1737550676967796</v>
+        <v>0.2742700992377391</v>
       </c>
       <c r="H4">
-        <v>0.1737550676967796</v>
+        <v>0.2742700992377391</v>
       </c>
       <c r="I4">
-        <v>0.1229729903449985</v>
+        <v>0.3044728894002589</v>
       </c>
       <c r="J4">
-        <v>0.1229729903449985</v>
+        <v>0.3044728894002589</v>
       </c>
       <c r="K4">
-        <v>314.7</v>
+        <v>210.3</v>
       </c>
       <c r="L4">
-        <v>0.1203625793620439</v>
+        <v>0.3024593700560909</v>
       </c>
       <c r="M4">
-        <v>139.5</v>
+        <v>82.5</v>
       </c>
       <c r="N4">
-        <v>0.05255424954792044</v>
+        <v>0.08960573476702509</v>
       </c>
       <c r="O4">
-        <v>0.4432793136320305</v>
+        <v>0.3922967189728959</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>59.4</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.06451612903225806</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.282453637660485</v>
       </c>
       <c r="S4">
-        <v>139.5</v>
+        <v>23.1</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0.28</v>
       </c>
       <c r="U4">
-        <v>640.7</v>
+        <v>260.2</v>
       </c>
       <c r="V4">
-        <v>0.2413728149487643</v>
+        <v>0.2826110568046052</v>
       </c>
       <c r="W4">
-        <v>0.1535121951219512</v>
+        <v>0.22930978083088</v>
       </c>
       <c r="X4">
-        <v>0.1193599822142334</v>
+        <v>0.1043697430233601</v>
       </c>
       <c r="Y4">
-        <v>0.03415221290771778</v>
+        <v>0.1249400378075198</v>
       </c>
       <c r="Z4">
-        <v>1.118270803782044</v>
+        <v>0.8679315940581699</v>
       </c>
       <c r="AA4">
-        <v>0.137517104756583</v>
+        <v>0.2642616402446636</v>
       </c>
       <c r="AB4">
-        <v>0.1084531701758685</v>
+        <v>0.1042787410608856</v>
       </c>
       <c r="AC4">
-        <v>0.02906393458071449</v>
+        <v>0.1599828991837779</v>
       </c>
       <c r="AD4">
-        <v>660.5</v>
+        <v>1.9</v>
       </c>
       <c r="AE4">
-        <v>24.37409721983432</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>684.8740972198343</v>
+        <v>1.9</v>
       </c>
       <c r="AG4">
-        <v>44.17409721983427</v>
+        <v>-258.3</v>
       </c>
       <c r="AH4">
-        <v>0.2050966998456452</v>
+        <v>0.002059397355300238</v>
       </c>
       <c r="AI4">
-        <v>0.2025431311439151</v>
+        <v>0.001806942463147884</v>
       </c>
       <c r="AJ4">
-        <v>0.01636942163839191</v>
+        <v>-0.389945652173913</v>
       </c>
       <c r="AK4">
-        <v>0.0161179679352043</v>
+        <v>-0.3264248704663213</v>
       </c>
       <c r="AL4">
-        <v>69.8</v>
+        <v>0.1</v>
       </c>
       <c r="AM4">
-        <v>69.8</v>
+        <v>0.1</v>
       </c>
       <c r="AN4">
-        <v>1.952986398580721</v>
+        <v>0.008958038661008957</v>
       </c>
       <c r="AO4">
-        <v>4.580229226361031</v>
+        <v>2117</v>
       </c>
       <c r="AP4">
-        <v>0.1306153081603615</v>
+        <v>-1.217821782178218</v>
       </c>
       <c r="AQ4">
-        <v>4.580229226361031</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enstar Group Limited (NasdaqGS:ESGR)</t>
+          <t>Brookfield Wealth Solutions Ltd. (NYSE:BNT)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -992,122 +989,649 @@
           <t>Reinsurance</t>
         </is>
       </c>
-      <c r="D5">
-        <v>-0.112</v>
-      </c>
-      <c r="E5">
-        <v>0.103</v>
-      </c>
       <c r="G5">
-        <v>0.7282099343955014</v>
+        <v>0.09735340877209389</v>
       </c>
       <c r="H5">
-        <v>0.7282099343955014</v>
+        <v>0.09735340877209389</v>
       </c>
       <c r="I5">
-        <v>0.6607310215557638</v>
+        <v>0.1529037688207238</v>
       </c>
       <c r="J5">
-        <v>0.6607310215557638</v>
+        <v>0.1529037688207238</v>
       </c>
       <c r="K5">
-        <v>1028</v>
+        <v>1106</v>
       </c>
       <c r="L5">
-        <v>0.9634489222118088</v>
+        <v>0.1034321518750585</v>
       </c>
       <c r="M5">
-        <v>191</v>
+        <v>65.351</v>
       </c>
       <c r="N5">
-        <v>0.04043782948362373</v>
+        <v>0.006611462390611563</v>
       </c>
       <c r="O5">
-        <v>0.1857976653696498</v>
+        <v>0.0590877034358047</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>53.351</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.005397440437047903</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.0482377938517179</v>
       </c>
       <c r="S5">
-        <v>191</v>
+        <v>12</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0.1836238160089364</v>
       </c>
       <c r="U5">
-        <v>572</v>
+        <v>14627</v>
       </c>
       <c r="V5">
-        <v>0.1211017720661402</v>
+        <v>1.479791592897971</v>
       </c>
       <c r="W5">
-        <v>0.2146585926080601</v>
+        <v>0.2674727932285369</v>
       </c>
       <c r="X5">
-        <v>0.1269650765413203</v>
+        <v>0.1569890450044459</v>
       </c>
       <c r="Y5">
-        <v>0.08769351606673986</v>
+        <v>0.110483748224091</v>
       </c>
       <c r="Z5">
-        <v>0.1717919819674771</v>
+        <v>1.695149017121116</v>
       </c>
       <c r="AA5">
-        <v>0.1135082917404605</v>
+        <v>0.2591946734305643</v>
       </c>
       <c r="AB5">
-        <v>0.1095797802265419</v>
+        <v>0.1127306085919704</v>
       </c>
       <c r="AC5">
-        <v>0.003928511513918542</v>
+        <v>0.1464640648385939</v>
       </c>
       <c r="AD5">
-        <v>1833</v>
+        <v>8919</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
+        <v>8919</v>
+      </c>
+      <c r="AG5">
+        <v>-5708</v>
+      </c>
+      <c r="AH5">
+        <v>0.4743265881351876</v>
+      </c>
+      <c r="AI5">
+        <v>0.4077816386247257</v>
+      </c>
+      <c r="AJ5">
+        <v>-1.366694600742248</v>
+      </c>
+      <c r="AK5">
+        <v>-0.7878536922015182</v>
+      </c>
+      <c r="AL5">
+        <v>334</v>
+      </c>
+      <c r="AM5">
+        <v>334</v>
+      </c>
+      <c r="AN5">
+        <v>4.919470490899062</v>
+      </c>
+      <c r="AO5">
+        <v>4.895209580838324</v>
+      </c>
+      <c r="AP5">
+        <v>-3.148372862658577</v>
+      </c>
+      <c r="AQ5">
+        <v>4.895209580838324</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Everest Group, Ltd. (NYSE:EG)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Reinsurance</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.159</v>
+      </c>
+      <c r="E6">
+        <v>0.468</v>
+      </c>
+      <c r="F6">
+        <v>0.008030000000000001</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0.1697080577377925</v>
+      </c>
+      <c r="J6">
+        <v>0.1697080577377925</v>
+      </c>
+      <c r="K6">
+        <v>2770</v>
+      </c>
+      <c r="L6">
+        <v>0.168527362881392</v>
+      </c>
+      <c r="M6">
+        <v>550</v>
+      </c>
+      <c r="N6">
+        <v>0.03530620105276672</v>
+      </c>
+      <c r="O6">
+        <v>0.1985559566787004</v>
+      </c>
+      <c r="P6">
+        <v>325</v>
+      </c>
+      <c r="Q6">
+        <v>0.02086275516754397</v>
+      </c>
+      <c r="R6">
+        <v>0.1173285198555957</v>
+      </c>
+      <c r="S6">
+        <v>225</v>
+      </c>
+      <c r="T6">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="U6">
+        <v>1599</v>
+      </c>
+      <c r="V6">
+        <v>0.1026447554243164</v>
+      </c>
+      <c r="W6">
+        <v>0.2467486192766791</v>
+      </c>
+      <c r="X6">
+        <v>0.1174655288483045</v>
+      </c>
+      <c r="Y6">
+        <v>0.1292830904283747</v>
+      </c>
+      <c r="Z6">
+        <v>1.296103936056466</v>
+      </c>
+      <c r="AA6">
+        <v>0.219959281614451</v>
+      </c>
+      <c r="AB6">
+        <v>0.10690125756672</v>
+      </c>
+      <c r="AC6">
+        <v>0.113058024047731</v>
+      </c>
+      <c r="AD6">
+        <v>3387</v>
+      </c>
+      <c r="AE6">
+        <v>135.4675449638647</v>
+      </c>
+      <c r="AF6">
+        <v>3522.467544963865</v>
+      </c>
+      <c r="AG6">
+        <v>1923.467544963865</v>
+      </c>
+      <c r="AH6">
+        <v>0.1844178702260416</v>
+      </c>
+      <c r="AI6">
+        <v>0.1867943050446658</v>
+      </c>
+      <c r="AJ6">
+        <v>0.1099032146888363</v>
+      </c>
+      <c r="AK6">
+        <v>0.1114506568994386</v>
+      </c>
+      <c r="AL6">
+        <v>147</v>
+      </c>
+      <c r="AM6">
+        <v>147</v>
+      </c>
+      <c r="AN6">
+        <v>141.125</v>
+      </c>
+      <c r="AO6">
+        <v>18.99659863945578</v>
+      </c>
+      <c r="AP6">
+        <v>80.14448104016104</v>
+      </c>
+      <c r="AQ6">
+        <v>18.99659863945578</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SiriusPoint Ltd. (NYSE:SPNT)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Reinsurance</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.318</v>
+      </c>
+      <c r="G7">
+        <v>0.1737550676967796</v>
+      </c>
+      <c r="H7">
+        <v>0.1737550676967796</v>
+      </c>
+      <c r="I7">
+        <v>0.1229729903449985</v>
+      </c>
+      <c r="J7">
+        <v>0.1229729903449985</v>
+      </c>
+      <c r="K7">
+        <v>314.7</v>
+      </c>
+      <c r="L7">
+        <v>0.1203625793620439</v>
+      </c>
+      <c r="M7">
+        <v>139.5</v>
+      </c>
+      <c r="N7">
+        <v>0.05255424954792044</v>
+      </c>
+      <c r="O7">
+        <v>0.4432793136320305</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>139.5</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>640.7</v>
+      </c>
+      <c r="V7">
+        <v>0.2413728149487643</v>
+      </c>
+      <c r="W7">
+        <v>0.1535121951219512</v>
+      </c>
+      <c r="X7">
+        <v>0.1193298553146371</v>
+      </c>
+      <c r="Y7">
+        <v>0.03418233980731417</v>
+      </c>
+      <c r="Z7">
+        <v>1.118270803782044</v>
+      </c>
+      <c r="AA7">
+        <v>0.137517104756583</v>
+      </c>
+      <c r="AB7">
+        <v>0.1084292222039559</v>
+      </c>
+      <c r="AC7">
+        <v>0.02908788255262706</v>
+      </c>
+      <c r="AD7">
+        <v>660.5</v>
+      </c>
+      <c r="AE7">
+        <v>24.37409721983432</v>
+      </c>
+      <c r="AF7">
+        <v>684.8740972198343</v>
+      </c>
+      <c r="AG7">
+        <v>44.17409721983427</v>
+      </c>
+      <c r="AH7">
+        <v>0.2050966998456452</v>
+      </c>
+      <c r="AI7">
+        <v>0.2025431311439151</v>
+      </c>
+      <c r="AJ7">
+        <v>0.01636942163839191</v>
+      </c>
+      <c r="AK7">
+        <v>0.0161179679352043</v>
+      </c>
+      <c r="AL7">
+        <v>69.8</v>
+      </c>
+      <c r="AM7">
+        <v>69.8</v>
+      </c>
+      <c r="AN7">
+        <v>1.952986398580721</v>
+      </c>
+      <c r="AO7">
+        <v>4.580229226361031</v>
+      </c>
+      <c r="AP7">
+        <v>0.1306153081603615</v>
+      </c>
+      <c r="AQ7">
+        <v>4.580229226361031</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Enstar Group Limited (NasdaqGS:ESGR)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Reinsurance</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>-0.112</v>
+      </c>
+      <c r="E8">
+        <v>0.103</v>
+      </c>
+      <c r="G8">
+        <v>0.7282099343955014</v>
+      </c>
+      <c r="H8">
+        <v>0.7282099343955014</v>
+      </c>
+      <c r="I8">
+        <v>0.6607310215557638</v>
+      </c>
+      <c r="J8">
+        <v>0.6607310215557638</v>
+      </c>
+      <c r="K8">
+        <v>1028</v>
+      </c>
+      <c r="L8">
+        <v>0.9634489222118088</v>
+      </c>
+      <c r="M8">
+        <v>191</v>
+      </c>
+      <c r="N8">
+        <v>0.04043782948362373</v>
+      </c>
+      <c r="O8">
+        <v>0.1857976653696498</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>191</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>572</v>
+      </c>
+      <c r="V8">
+        <v>0.1211017720661402</v>
+      </c>
+      <c r="W8">
+        <v>0.2146585926080601</v>
+      </c>
+      <c r="X8">
+        <v>0.1269318349330696</v>
+      </c>
+      <c r="Y8">
+        <v>0.08772675767499055</v>
+      </c>
+      <c r="Z8">
+        <v>0.1717919819674771</v>
+      </c>
+      <c r="AA8">
+        <v>0.1135082917404605</v>
+      </c>
+      <c r="AB8">
+        <v>0.1095558322546294</v>
+      </c>
+      <c r="AC8">
+        <v>0.003952459485831117</v>
+      </c>
+      <c r="AD8">
         <v>1833</v>
       </c>
-      <c r="AG5">
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>1833</v>
+      </c>
+      <c r="AG8">
         <v>1261</v>
       </c>
-      <c r="AH5">
+      <c r="AH8">
         <v>0.2795784207556091</v>
       </c>
-      <c r="AI5">
+      <c r="AI8">
         <v>0.231089258698941</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ8">
         <v>0.2107180455525291</v>
       </c>
-      <c r="AK5">
+      <c r="AK8">
         <v>0.1713315217391304</v>
       </c>
-      <c r="AL5">
+      <c r="AL8">
         <v>90</v>
       </c>
-      <c r="AM5">
+      <c r="AM8">
         <v>90</v>
       </c>
-      <c r="AN5">
+      <c r="AN8">
         <v>2.573353923908466</v>
       </c>
-      <c r="AO5">
+      <c r="AO8">
         <v>7.833333333333333</v>
       </c>
-      <c r="AP5">
+      <c r="AP8">
         <v>1.770321493752632</v>
       </c>
-      <c r="AQ5">
+      <c r="AQ8">
         <v>7.833333333333333</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Maiden Holdings, Ltd. (NasdaqCM:MHLD)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Reinsurance</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>-0.387</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>-0.4303489809457072</v>
+      </c>
+      <c r="J9">
+        <v>-0.4303489809457072</v>
+      </c>
+      <c r="K9">
+        <v>-63.8</v>
+      </c>
+      <c r="L9">
+        <v>-0.7160493827160493</v>
+      </c>
+      <c r="M9">
+        <v>4.18</v>
+      </c>
+      <c r="N9">
+        <v>0.02488095238095238</v>
+      </c>
+      <c r="O9">
+        <v>-0.06551724137931034</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>4.18</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>110</v>
+      </c>
+      <c r="V9">
+        <v>0.6547619047619048</v>
+      </c>
+      <c r="W9">
+        <v>-0.2424012158054711</v>
+      </c>
+      <c r="X9">
+        <v>0.1929406165034469</v>
+      </c>
+      <c r="Y9">
+        <v>-0.435341832308918</v>
+      </c>
+      <c r="Z9">
+        <v>0.1781552933503453</v>
+      </c>
+      <c r="AA9">
+        <v>-0.07666894894340463</v>
+      </c>
+      <c r="AB9">
+        <v>0.1165341804605612</v>
+      </c>
+      <c r="AC9">
+        <v>-0.1932031294039659</v>
+      </c>
+      <c r="AD9">
+        <v>254.7</v>
+      </c>
+      <c r="AE9">
+        <v>0.2254710113125605</v>
+      </c>
+      <c r="AF9">
+        <v>254.9254710113125</v>
+      </c>
+      <c r="AG9">
+        <v>144.9254710113125</v>
+      </c>
+      <c r="AH9">
+        <v>0.6027668903500345</v>
+      </c>
+      <c r="AI9">
+        <v>0.5504458013389758</v>
+      </c>
+      <c r="AJ9">
+        <v>0.4631309510949761</v>
+      </c>
+      <c r="AK9">
+        <v>0.4104078660660244</v>
+      </c>
+      <c r="AL9">
+        <v>19.2</v>
+      </c>
+      <c r="AM9">
+        <v>19.2</v>
+      </c>
+      <c r="AN9">
+        <v>1267.164179104477</v>
+      </c>
+      <c r="AO9">
+        <v>-2.005208333333333</v>
+      </c>
+      <c r="AP9">
+        <v>721.0222438373758</v>
+      </c>
+      <c r="AQ9">
+        <v>-2.005208333333333</v>
       </c>
     </row>
   </sheetData>
